--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/90_workbooks/ISMS-IMP-A.5.31.6_Compliance_Dashboard_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.31-legal-statutory-regulatory-contractual-requirements/WKBK/90_workbooks/ISMS-IMP-A.5.31.6_Compliance_Dashboard_20260208.xlsx
@@ -601,7 +601,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Last Updated: 08.02.2026 11:49</t>
+          <t>Last Updated: 08.02.2026 12:25</t>
         </is>
       </c>
     </row>
